--- a/site/exports/csu-xiangya-public-health.xlsx
+++ b/site/exports/csu-xiangya-public-health.xlsx
@@ -926,7 +926,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L8" s="2" t="b">
